--- a/results_base_case.xlsx
+++ b/results_base_case.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -2782,7 +2782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2958,40 +2958,85 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
+          <t>JU</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>JI</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>penalty_U</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>penalty_lines</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>penalty_trafo</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>objective_profile</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>J_used_total</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>J_used_component_1</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>J_used_component_2</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>J_used_component_3</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>J_used_component_4</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>J_used_component_5</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>constraint_violations</t>
         </is>
@@ -3100,18 +3145,45 @@
       <c r="AH2" t="n">
         <v>6.911300462678608</v>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" t="n">
+        <v>0.08676401264531347</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.040346978090067</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.3948902431234372</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.482568845046053</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>6077.615937021928</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>607761.6665410951</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>607761.9664225607</v>
+      </c>
+      <c r="AR2" t="inlineStr">
         <is>
           <t>base_case</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>U:100:L3:1.1328;U:101:L3:1.1324;U:102:L3:1.1334;U:103:L3:1.1288;U:104:L3:1.1343;U:105:L3:1.1285;U:106:L3:1.1284;U:107:L3:1.1289;U:108:L3:1.1322;U:109:L3:1.1334;U:110:L3:1.1321;U:111:L3:1.1335;U:112:L3:1.1339;U:113:L3:1.1342;U:114:L3:1.1318;U:115:L3:1.1343;U:116:L3:1.1330;U:32:L3:1.1013;U:35:L3:1.1068;U:38:L3:1.1084;U:41:L3:1.1098;U:43:L3:1.1112;U:44:L3:1.1085;U:45:L3:1.1097;U:46:L3:1.1015;U:47:L3:1.1085;U:48:L3:1.1107;U:50:L3:1.1091;U:51:L3:1.1144;U:52:L3:1.1111;U:53:L3:1.1127;U:54:L3:1.1108;U:55:L3:1.1136;U:56:L3:1.1134;U:57:L3:1.1130;U:58:L3:1.1176;U:59:L3:1.1150;U:60:L3:1.1180;U:61:L3:1.1147;U:62:L3:1.1155;U:63:L3:1.1153;U:64:L3:1.1147;U:65:L3:1.1154;U:66:L3:1.1161;U:67:L3:1.1133;U:68:L3:1.1209;U:69:L3:1.1150;U:70:L3:1.1149;U:71:L3:1.1236;U:72:L3:1.1157;U:73:L3:1.1237;U:74:L3:1.1259;U:75:L3:1.1149;U:76:L3:1.1129;U:77:L3:1.1149;U:78:L3:1.1158;U:79:L3:1.1283;U:80:L3:1.1162;U:81:L3:1.1166;U:82:L3:1.1302;U:83:L3:1.1258;U:84:L3:1.1305;U:85:L3:1.1311;U:86:L3:1.1322;U:87:L3:1.1309;U:88:L3:1.1311;U:89:L3:1.1333;U:90:L3:1.1335;U:91:L3:1.1335;U:92:L3:1.1335;U:93:L3:1.1339;U:94:L3:1.1336;U:95:L3:1.1312;U:96:L3:1.1331;U:97:L3:1.1211;U:98:L3:1.1284;U:99:L3:1.1333</t>
         </is>
